--- a/docs/inventario-title-description.xlsx
+++ b/docs/inventario-title-description.xlsx
@@ -1161,11 +1161,11 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>A rotina de limpeza e secagem que faz o calçado de trabalho durar, o que nunca fazer com couro e solado, e por que alternar pares rende mais que qualquer produto.</t>
+          <t>Como limpar e conservar calçado de segurança: a rotina de dois minutos, o que nunca fazer com couro e solado, e por que alternar pares faz durar mais.</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="I13" s="5">
         <f>IF(H12=0,"sem description",IF(H12&gt;160,"longa",IF(H12&lt;120,"curta","ok")))</f>
@@ -1377,11 +1377,11 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Por que EPI para eletricidade é uma compra diferente, o que a aparência não mostra, e o que precisa estar definido antes de pedir orçamento. Sem substituir a análise de risco.</t>
+          <t>EPI para eletricista: por que a escolha muda, o que a aparência do equipamento não mostra e o que definir antes de pedir o orçamento.</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="I17" s="5">
         <f>IF(H16=0,"sem description",IF(H16&gt;160,"longa",IF(H16&lt;120,"curta","ok")))</f>
@@ -1863,11 +1863,11 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>As causas reais da recusa de EPI, o que fazer em cada uma e como registrar — a leitura operacional, com o que a NR-6 coloca do lado do trabalhador e do empregador.</t>
+          <t>Funcionário se recusa a usar EPI: as cinco causas mais comuns, o que fazer em cada uma, como registrar e o que a NR-6 cobra de cada lado.</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="I26" s="5">
         <f>IF(H25=0,"sem description",IF(H25&gt;160,"longa",IF(H25&lt;120,"curta","ok")))</f>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>A conta tem três parcelas: reposição programada, troca eventual e entrada de pessoal. Como tirar o número do seu próprio histórico e o que fazer no primeiro ano.</t>
+          <t>Quantos pares de calçado por ano para a equipe: a conta tem três parcelas. Como tirar o número do seu histórico e o que fazer no primeiro ano.</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="I36" s="5">
         <f>IF(H35=0,"sem description",IF(H35&gt;160,"longa",IF(H35&lt;120,"curta","ok")))</f>
@@ -4823,11 +4823,11 @@
       </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
-          <t>O site só grava cookie de análise depois que você aceita, não tem cadastro e não guarda o que você escreve no formulário. Veja o que é tratado, por quê, e como exercer seus direitos.</t>
+          <t>O site só grava cookie de análise depois que você aceita, não tem cadastro e não guarda o que você escreve. Veja o que é tratado e seus direitos.</t>
         </is>
       </c>
       <c r="H88" s="9" t="n">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="I88" s="9">
         <f>IF(H87=0,"sem description",IF(H87&gt;160,"longa",IF(H87&lt;120,"curta","ok")))</f>
@@ -4925,7 +4925,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>Medido no build de 22/09/2026, em navegador real. Os valores da aba Inventário são os RENDERIZADOS, com o sufixo do site já somado.</t>
+          <t>Medido no build de 23/09/2026, em navegador real. Os valores da aba Inventário são os RENDERIZADOS, com o sufixo do site já somado.</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>O resumo acima é contagem por fórmula e aparece ao abrir o arquivo no Excel ou no Google Sheets. Os números foram conferidos por fora, um a um, antes da entrega.</t>
+          <t>O resumo acima é contagem por fórmula e aparece ao abrir no Excel ou no Google Sheets. Os números foram conferidos por fora antes da entrega.</t>
         </is>
       </c>
     </row>
